--- a/exam_forms/003_telecommunication_systems_knowledge_quiz--exam_forms.xlsx
+++ b/exam_forms/003_telecommunication_systems_knowledge_quiz--exam_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="47" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>form_1</t>
+          <t>question_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Telecommunication Systems</t>
+          <t>What is the primary function of a telecommunication system?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,7 +538,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>What is Telecommunication</t>
+          <t>What are the different types of telecommunication systems?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,7 +561,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>What is telecommunica</t>
+          <t>Which of the following telecommunication systems is used for internet connectivity?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>What type of telecommunication system</t>
+          <t>What is your area of expertise in telecommunication systems?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Which of the following</t>
+          <t>How would you rate your level of knowledge in telecommunication systems?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,7 +630,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>What is your role in telecommunication system</t>
+          <t>Which of the following telecommunication systems is used for wireless connectivity?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,7 +653,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>What is your level of knowledge</t>
+          <t>What is the difference between a LAN and a WAN telecommunication system?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,7 +676,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>What is your area of expertise</t>
+          <t>Which of the following is a type of telecommunication system used for data transmission?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,7 +699,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>What is the type of telecommu</t>
+          <t>What is your role in a telecommunication system?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,7 +722,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>telecommu</t>
+          <t>How many devices can a hub connect?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,7 +745,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>telecommu</t>
+          <t>Which of the following is used for network segmentation?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,7 +768,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>telecommu</t>
+          <t>How often do you update your knowledge on telecommunication systems?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>telecommu</t>
+          <t>What is the purpose of a network protocol?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>telecommu</t>
+          <t>What is the difference between a router and a switch?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>telecommu</t>
+          <t>What is the primary function of a network interface?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>telecommu</t>
+          <t>What is the purpose of a network cable?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>telecommu</t>
+          <t>What is the difference between a LAN and a WAN?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>telecommu</t>
+          <t>What is the purpose of a network hub?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>telecommu</t>
+          <t>What is the purpose of a network repeater?</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>telecommu</t>
+          <t>What is the purpose of a network bridge?</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>telecommu</t>
+          <t>What is the purpose of a network switch?</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>telecommu</t>
+          <t>What is the purpose of a network router?</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>telecommu</t>
+          <t>What is the purpose of a network firewall?</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>telecommu</t>
+          <t>What is the purpose of a network intrusion detection system?</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1077,11 +1077,126 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>telecommu</t>
+          <t>What is the purpose of a network access control system?</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>question_26</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>What is the purpose of a network management system?</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>question_27</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>What is the purpose of a network monitoring system?</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>question_28</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>What is the purpose of a network performance monitor?</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>question_29</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>What is the purpose of a network quality of service (QoS) manager?</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>question_30</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>What is the purpose of a network configuration manager?</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +1213,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1246,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'option1':_2.1,_'label':_'radio1',_'value':_'radio1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'option1': 2.1, 'label': 'Radio1', 'value': 'radio1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1148,233 +1263,233 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'option2':_2.2,_'label':_'radio2',_'value':_'radio2'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'option2': 2.2, 'label': 'Radio2', 'value': 'radio2'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'option1':_4.1,_'label':_'option1',_'value':_'option1'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'option1': 4.1, 'label': 'Option1', 'value': 'option1'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'option2':_4.2,_'label':_'option2',_'value':_'option2'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'option2': 4.2, 'label': 'Option2', 'value': 'option2'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'option3':_4.3,_'label':_'option3',_'value':_'option4'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'option3': 4.3, 'label': 'Option3', 'value': 'option4'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>question_5_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'option1':_5.1,_'label':_'option1',_'value':_'option1'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'option1': 5.1, 'label': 'Option1', 'value': 'option1'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>question_5_choices</t>
+          <t>question_4_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'option2':_5.2,_'label':_'option2',_'value':_'option1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'option2': 5.2, 'label': 'Option2', 'value': 'option1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>question_5_choices</t>
+          <t>question_4_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'option3':_5.3,_'label':_'option3',_'value':_'option3'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'option3': 5.3, 'label': 'Option3', 'value': 'option3'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>question_6_choices</t>
+          <t>question_4_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'option1':_6.1,_'label':_'option1',_'value':_'option1'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'option1': 6.1, 'label': 'Option1', 'value': 'option1'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>question_6_choices</t>
+          <t>question_5_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'option2':_6.2,_'label':_'option2',_'value':_'option1'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'option2': 6.2, 'label': 'Option2', 'value': 'option1'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>question_6_choices</t>
+          <t>question_5_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'option3':_6.3,_'label':_'option3',_'value':_'option3'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'option3': 6.3, 'label': 'Option3', 'value': 'option3'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>question_7_choices</t>
+          <t>question_5_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'option1':_7.1,_'label':_'level1',_'value':_'level1'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'option1': 7.1, 'label': 'Level1', 'value': 'level1'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>question_7_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'option2':_7.2,_'label':_'level2',_'value':_'level2'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'option2': 7.2, 'label': 'Level2', 'value': 'level2'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>question_8_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'option1':_8.1,_'label':_'option1',_'value':_'option1'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'option1': 8.1, 'label': 'Option1', 'value': 'option1'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>question_8_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'option2':_8.2,_'label':_'option2',_'value':_'option2'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'option2': 8.2, 'label': 'Option2', 'value': 'option2'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1501,250 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'option3':_8.3,_'label':_'option3',_'value':_'option3'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'option3': 8.3, 'label': 'Option3', 'value': 'option3'}</t>
+          <t>Option 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>question_8_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>option_2</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Option 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>question_8_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>option_3</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Option 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>question_9_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>option_1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Option 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>question_9_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>option_2</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Option 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>question_9_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>option_3</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Option 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>question_10_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>option_1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Option 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>question_10_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>option_2</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Option 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>question_10_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>option_3</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Option 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>question_11_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>option_1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Option 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>question_11_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>option_2</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Option 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>question_11_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>option_3</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Option 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>question_12_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>option_1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Option 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>question_12_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>option_2</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Option 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>question_12_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>option_3</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
